--- a/website/examples/example_odk_calibrated_scale.xlsx
+++ b/website/examples/example_odk_calibrated_scale.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R186cdc0bfd204f7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rb9e074898ac14658"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R25aca2c5021447ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R5bf5f16509004f05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R0fc93bc41ce14a33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R89d2d285cc024bd7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -550,7 +550,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='calibrated_scale',input_prompt='Rate your pain',input_hint='0 means no pain; 100 means the worst pain you can imagine',input_vas_length_mm='50',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='calibrated_scale',input_prompt='Rate your pain',input_hint='0 means no pain; 100 means the worst pain you can imagine',input_vas_length_mm='50',return_mode='flat')</x:v>
       </x:c>
       <x:c r="J3"/>
       <x:c r="K3"/>
@@ -560,10 +560,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D4"/>
       <x:c r="E4"/>
@@ -581,10 +581,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D5"/>
       <x:c r="E5"/>
